--- a/www/flightdata/xlsx/eoss-328.xlsx
+++ b/www/flightdata/xlsx/eoss-328.xlsx
@@ -2931,7 +2931,7 @@
         <v>26934.87</v>
       </c>
       <c r="I2">
-        <v>465</v>
+        <v>352</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
